--- a/WRE01N.xlsx
+++ b/WRE01N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="35">
   <si>
     <t/>
   </si>
@@ -40,6 +40,15 @@
     <t>2</t>
   </si>
   <si>
+    <t>10037228</t>
+  </si>
+  <si>
+    <t>BYCLN PMTH RGLR 200</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>20087027</t>
   </si>
   <si>
@@ -61,9 +70,6 @@
     <t>EKONOMI EL-500K 145G</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
@@ -74,6 +80,12 @@
   </si>
   <si>
     <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20086179</t>
+  </si>
+  <si>
+    <t>SKLN MGNLIA BRIES225</t>
   </si>
   <si>
     <t>20053858</t>
@@ -496,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -577,13 +589,13 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -600,18 +612,18 @@
         <v>8</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -620,50 +632,50 @@
         <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -677,53 +689,93 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
